--- a/data/availability/projects/palm-hills-developments/palm-parks.xlsx
+++ b/data/availability/projects/palm-hills-developments/palm-parks.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for palm-parks</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -759,7 +769,6 @@
       <c r="G2" t="n">
         <v>132.38</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -816,7 +825,6 @@
       <c r="G3" t="n">
         <v>170.1</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -873,7 +881,6 @@
       <c r="G4" t="n">
         <v>169.67</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -930,7 +937,6 @@
       <c r="G5" t="n">
         <v>169.71</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -987,7 +993,6 @@
       <c r="G6" t="n">
         <v>168.52</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1044,7 +1049,6 @@
       <c r="G7" t="n">
         <v>170.19</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1101,7 +1105,6 @@
       <c r="G8" t="n">
         <v>132.38</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1158,7 +1161,6 @@
       <c r="G9" t="n">
         <v>169.26</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/palm-parks.xlsx
+++ b/data/availability/projects/palm-hills-developments/palm-parks.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
